--- a/excel/odpfasi.xlsx
+++ b/excel/odpfasi.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K382"/>
+  <dimension ref="A1:K425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8057,7 +8057,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>37321</v>
+        <v>37330</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -8067,31 +8067,31 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="I178" t="n">
-        <v>15</v>
+        <v>0.667</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8100,41 +8100,41 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>37321</v>
+        <v>37330</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D179" t="n">
         <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="H179" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="I179" t="n">
-        <v>15</v>
+        <v>5.25</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8143,41 +8143,41 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>37321</v>
+        <v>37330</v>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="H180" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="I180" t="n">
-        <v>15</v>
+        <v>1.25</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>CABLAGGIO</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8186,41 +8186,41 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>37321</v>
+        <v>37330</v>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D181" t="n">
         <v>1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="H181" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="I181" t="n">
-        <v>15</v>
+        <v>1.25</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>CABLAGGIO</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>37330</v>
+        <v>37346</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -8254,7 +8254,7 @@
         <v>45973</v>
       </c>
       <c r="I182" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8272,10 +8272,10 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>37330</v>
+        <v>37346</v>
       </c>
       <c r="C183" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
@@ -8297,7 +8297,7 @@
         <v>45973</v>
       </c>
       <c r="I183" t="n">
-        <v>5.25</v>
+        <v>0.333</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8315,17 +8315,17 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>37330</v>
+        <v>37347</v>
       </c>
       <c r="C184" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8340,11 +8340,11 @@
         <v>45973</v>
       </c>
       <c r="I184" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>CABLAGGIO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -8358,22 +8358,22 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>37330</v>
+        <v>37347</v>
       </c>
       <c r="C185" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G185" s="2" t="n">
@@ -8383,11 +8383,11 @@
         <v>45973</v>
       </c>
       <c r="I185" t="n">
-        <v>1.25</v>
+        <v>0.55</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>CABLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -8401,10 +8401,10 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>37346</v>
+        <v>37347</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D186" t="n">
         <v>1</v>
@@ -8426,7 +8426,7 @@
         <v>45973</v>
       </c>
       <c r="I186" t="n">
-        <v>0.333</v>
+        <v>2.42</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -8444,22 +8444,22 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>37346</v>
+        <v>37347</v>
       </c>
       <c r="C187" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G187" s="2" t="n">
@@ -8469,11 +8469,11 @@
         <v>45973</v>
       </c>
       <c r="I187" t="n">
-        <v>0.333</v>
+        <v>0.55</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -8487,7 +8487,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>37347</v>
+        <v>37410</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -8506,13 +8506,13 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="I188" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -8530,36 +8530,36 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>37347</v>
+        <v>37425</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="I189" t="n">
-        <v>0.55</v>
+        <v>4</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>CABLAGGIO</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -8573,10 +8573,10 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>37347</v>
+        <v>37426</v>
       </c>
       <c r="C190" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="I190" t="n">
-        <v>2.42</v>
+        <v>3.51</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -8616,10 +8616,10 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>37347</v>
+        <v>37426</v>
       </c>
       <c r="C191" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D191" t="n">
         <v>2</v>
@@ -8635,13 +8635,13 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="I191" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -8659,10 +8659,10 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>37410</v>
+        <v>37426</v>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="D192" t="n">
         <v>1</v>
@@ -8684,7 +8684,7 @@
         <v>45974</v>
       </c>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>3.53</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -8702,22 +8702,22 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>37425</v>
+        <v>37426</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G193" s="2" t="n">
@@ -8727,11 +8727,11 @@
         <v>45974</v>
       </c>
       <c r="I193" t="n">
-        <v>4</v>
+        <v>0.45</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>CABLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -8748,7 +8748,7 @@
         <v>37426</v>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="D194" t="n">
         <v>1</v>
@@ -8770,7 +8770,7 @@
         <v>45974</v>
       </c>
       <c r="I194" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>37426</v>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="D195" t="n">
         <v>2</v>
@@ -8834,7 +8834,7 @@
         <v>37426</v>
       </c>
       <c r="C196" t="n">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
@@ -8856,7 +8856,7 @@
         <v>45974</v>
       </c>
       <c r="I196" t="n">
-        <v>3.53</v>
+        <v>4.25</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>37426</v>
       </c>
       <c r="C197" t="n">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="D197" t="n">
         <v>2</v>
@@ -8899,7 +8899,7 @@
         <v>45974</v>
       </c>
       <c r="I197" t="n">
-        <v>0.45</v>
+        <v>0.417</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>37426</v>
+        <v>37453</v>
       </c>
       <c r="C198" t="n">
-        <v>214</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
         <v>1</v>
@@ -8936,13 +8936,13 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="I198" t="n">
-        <v>3.05</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -8960,36 +8960,36 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>37426</v>
+        <v>37459</v>
       </c>
       <c r="C199" t="n">
-        <v>214</v>
+        <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="I199" t="n">
-        <v>0.45</v>
+        <v>1.583</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -9003,10 +9003,10 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>37426</v>
+        <v>37459</v>
       </c>
       <c r="C200" t="n">
-        <v>317</v>
+        <v>15</v>
       </c>
       <c r="D200" t="n">
         <v>1</v>
@@ -9022,13 +9022,13 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="I200" t="n">
-        <v>4.25</v>
+        <v>0.95</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9046,36 +9046,36 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>37426</v>
+        <v>37460</v>
       </c>
       <c r="C201" t="n">
-        <v>317</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="I201" t="n">
-        <v>0.417</v>
+        <v>2.46</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -9089,36 +9089,36 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>37453</v>
+        <v>37460</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.583</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -9132,10 +9132,10 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>37459</v>
+        <v>37460</v>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
@@ -9157,7 +9157,7 @@
         <v>45978</v>
       </c>
       <c r="I203" t="n">
-        <v>1.583</v>
+        <v>2.46</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9175,22 +9175,22 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>37459</v>
+        <v>37460</v>
       </c>
       <c r="C204" t="n">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G204" s="2" t="n">
@@ -9200,11 +9200,11 @@
         <v>45978</v>
       </c>
       <c r="I204" t="n">
-        <v>0.95</v>
+        <v>0.583</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -9221,7 +9221,7 @@
         <v>37460</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D205" t="n">
         <v>1</v>
@@ -9264,7 +9264,7 @@
         <v>37460</v>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D206" t="n">
         <v>2</v>
@@ -9307,7 +9307,7 @@
         <v>37460</v>
       </c>
       <c r="C207" t="n">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -9350,7 +9350,7 @@
         <v>37460</v>
       </c>
       <c r="C208" t="n">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="D208" t="n">
         <v>2</v>
@@ -9393,7 +9393,7 @@
         <v>37460</v>
       </c>
       <c r="C209" t="n">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="D209" t="n">
         <v>1</v>
@@ -9436,7 +9436,7 @@
         <v>37460</v>
       </c>
       <c r="C210" t="n">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="D210" t="n">
         <v>2</v>
@@ -9479,7 +9479,7 @@
         <v>37460</v>
       </c>
       <c r="C211" t="n">
-        <v>304</v>
+        <v>507</v>
       </c>
       <c r="D211" t="n">
         <v>1</v>
@@ -9522,7 +9522,7 @@
         <v>37460</v>
       </c>
       <c r="C212" t="n">
-        <v>304</v>
+        <v>507</v>
       </c>
       <c r="D212" t="n">
         <v>2</v>
@@ -9565,7 +9565,7 @@
         <v>37460</v>
       </c>
       <c r="C213" t="n">
-        <v>405</v>
+        <v>608</v>
       </c>
       <c r="D213" t="n">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         <v>37460</v>
       </c>
       <c r="C214" t="n">
-        <v>405</v>
+        <v>608</v>
       </c>
       <c r="D214" t="n">
         <v>2</v>
@@ -9651,7 +9651,7 @@
         <v>37460</v>
       </c>
       <c r="C215" t="n">
-        <v>507</v>
+        <v>709</v>
       </c>
       <c r="D215" t="n">
         <v>1</v>
@@ -9694,7 +9694,7 @@
         <v>37460</v>
       </c>
       <c r="C216" t="n">
-        <v>507</v>
+        <v>709</v>
       </c>
       <c r="D216" t="n">
         <v>2</v>
@@ -9734,10 +9734,10 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>37460</v>
+        <v>37466</v>
       </c>
       <c r="C217" t="n">
-        <v>608</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
         <v>1</v>
@@ -9759,7 +9759,7 @@
         <v>45978</v>
       </c>
       <c r="I217" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>37460</v>
+        <v>37466</v>
       </c>
       <c r="C218" t="n">
-        <v>608</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
         <v>2</v>
@@ -9802,7 +9802,7 @@
         <v>45978</v>
       </c>
       <c r="I218" t="n">
-        <v>0.583</v>
+        <v>0.45</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -9820,10 +9820,10 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>37460</v>
+        <v>37563</v>
       </c>
       <c r="C219" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
         <v>1</v>
@@ -9845,7 +9845,7 @@
         <v>45978</v>
       </c>
       <c r="I219" t="n">
-        <v>2.46</v>
+        <v>1.333</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -9863,36 +9863,36 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>37460</v>
+        <v>37636</v>
       </c>
       <c r="C220" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="I220" t="n">
-        <v>0.583</v>
+        <v>3.05</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -9906,36 +9906,36 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>37466</v>
+        <v>37636</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="I221" t="n">
-        <v>3.05</v>
+        <v>0.45</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -9949,41 +9949,41 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>37466</v>
+        <v>37775</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="I222" t="n">
-        <v>0.45</v>
+        <v>8</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9992,41 +9992,41 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>37563</v>
+        <v>37775</v>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="I223" t="n">
-        <v>1.333</v>
+        <v>8</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>37636</v>
+        <v>37780</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -10054,13 +10054,13 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="I224" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -10078,36 +10078,36 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>37636</v>
+        <v>37780</v>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="I225" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -10121,7 +10121,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>37775</v>
+        <v>37781</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -10131,31 +10131,31 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="I226" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -10164,41 +10164,41 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>37775</v>
+        <v>37781</v>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="I227" t="n">
-        <v>8</v>
+        <v>0.55</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>37780</v>
+        <v>37782</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -10232,7 +10232,7 @@
         <v>45981</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5</v>
+        <v>0.317</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -10250,10 +10250,10 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>37780</v>
+        <v>37783</v>
       </c>
       <c r="C229" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         <v>45981</v>
       </c>
       <c r="I229" t="n">
-        <v>0.333</v>
+        <v>2.46</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10293,22 +10293,22 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>37781</v>
+        <v>37783</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G230" s="2" t="n">
@@ -10318,11 +10318,11 @@
         <v>45981</v>
       </c>
       <c r="I230" t="n">
-        <v>2.42</v>
+        <v>0.583</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -10336,22 +10336,22 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>37781</v>
+        <v>37783</v>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G231" s="2" t="n">
@@ -10361,11 +10361,11 @@
         <v>45981</v>
       </c>
       <c r="I231" t="n">
-        <v>0.55</v>
+        <v>3.53</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -10379,22 +10379,22 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>37782</v>
+        <v>37783</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G232" s="2" t="n">
@@ -10404,11 +10404,11 @@
         <v>45981</v>
       </c>
       <c r="I232" t="n">
-        <v>0.317</v>
+        <v>0.45</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -10425,7 +10425,7 @@
         <v>37783</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="D233" t="n">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         <v>45981</v>
       </c>
       <c r="I233" t="n">
-        <v>2.46</v>
+        <v>3.53</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>37783</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="D234" t="n">
         <v>2</v>
@@ -10490,7 +10490,7 @@
         <v>45981</v>
       </c>
       <c r="I234" t="n">
-        <v>0.583</v>
+        <v>0.45</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>37783</v>
       </c>
       <c r="C235" t="n">
-        <v>102</v>
+        <v>316</v>
       </c>
       <c r="D235" t="n">
         <v>1</v>
@@ -10554,7 +10554,7 @@
         <v>37783</v>
       </c>
       <c r="C236" t="n">
-        <v>102</v>
+        <v>316</v>
       </c>
       <c r="D236" t="n">
         <v>2</v>
@@ -10597,7 +10597,7 @@
         <v>37783</v>
       </c>
       <c r="C237" t="n">
-        <v>209</v>
+        <v>423</v>
       </c>
       <c r="D237" t="n">
         <v>1</v>
@@ -10640,7 +10640,7 @@
         <v>37783</v>
       </c>
       <c r="C238" t="n">
-        <v>209</v>
+        <v>423</v>
       </c>
       <c r="D238" t="n">
         <v>2</v>
@@ -10680,10 +10680,10 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>37783</v>
+        <v>37912</v>
       </c>
       <c r="C239" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
         <v>1</v>
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="I239" t="n">
-        <v>3.53</v>
+        <v>0.333</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -10723,36 +10723,36 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>37783</v>
+        <v>37912</v>
       </c>
       <c r="C240" t="n">
-        <v>316</v>
+        <v>9</v>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="I240" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -10766,10 +10766,10 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>37783</v>
+        <v>37912</v>
       </c>
       <c r="C241" t="n">
-        <v>423</v>
+        <v>17</v>
       </c>
       <c r="D241" t="n">
         <v>1</v>
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="I241" t="n">
-        <v>3.53</v>
+        <v>0.167</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -10809,36 +10809,36 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>37783</v>
+        <v>37912</v>
       </c>
       <c r="C242" t="n">
-        <v>423</v>
+        <v>25</v>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="I242" t="n">
-        <v>0.45</v>
+        <v>0.167</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -10855,7 +10855,7 @@
         <v>37912</v>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D243" t="n">
         <v>1</v>
@@ -10898,7 +10898,7 @@
         <v>37912</v>
       </c>
       <c r="C244" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D244" t="n">
         <v>1</v>
@@ -10920,7 +10920,7 @@
         <v>45982</v>
       </c>
       <c r="I244" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -10938,10 +10938,10 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>37912</v>
+        <v>37913</v>
       </c>
       <c r="C245" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
         <v>1</v>
@@ -10963,7 +10963,7 @@
         <v>45982</v>
       </c>
       <c r="I245" t="n">
-        <v>0.167</v>
+        <v>1.53</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -10981,22 +10981,22 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>37912</v>
+        <v>37913</v>
       </c>
       <c r="C246" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G246" s="2" t="n">
@@ -11006,11 +11006,11 @@
         <v>45982</v>
       </c>
       <c r="I246" t="n">
-        <v>0.167</v>
+        <v>0.517</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -11024,10 +11024,10 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>37912</v>
+        <v>37913</v>
       </c>
       <c r="C247" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="D247" t="n">
         <v>1</v>
@@ -11049,7 +11049,7 @@
         <v>45982</v>
       </c>
       <c r="I247" t="n">
-        <v>0.333</v>
+        <v>1.53</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -11067,22 +11067,22 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>37912</v>
+        <v>37913</v>
       </c>
       <c r="C248" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G248" s="2" t="n">
@@ -11092,11 +11092,11 @@
         <v>45982</v>
       </c>
       <c r="I248" t="n">
-        <v>0.167</v>
+        <v>0.517</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -11113,7 +11113,7 @@
         <v>37913</v>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="D249" t="n">
         <v>1</v>
@@ -11156,7 +11156,7 @@
         <v>37913</v>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="D250" t="n">
         <v>2</v>
@@ -11199,7 +11199,7 @@
         <v>37913</v>
       </c>
       <c r="C251" t="n">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="D251" t="n">
         <v>1</v>
@@ -11242,7 +11242,7 @@
         <v>37913</v>
       </c>
       <c r="C252" t="n">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="D252" t="n">
         <v>2</v>
@@ -11285,7 +11285,7 @@
         <v>37913</v>
       </c>
       <c r="C253" t="n">
-        <v>171</v>
+        <v>341</v>
       </c>
       <c r="D253" t="n">
         <v>1</v>
@@ -11328,7 +11328,7 @@
         <v>37913</v>
       </c>
       <c r="C254" t="n">
-        <v>171</v>
+        <v>341</v>
       </c>
       <c r="D254" t="n">
         <v>2</v>
@@ -11371,7 +11371,7 @@
         <v>37913</v>
       </c>
       <c r="C255" t="n">
-        <v>256</v>
+        <v>426</v>
       </c>
       <c r="D255" t="n">
         <v>1</v>
@@ -11414,7 +11414,7 @@
         <v>37913</v>
       </c>
       <c r="C256" t="n">
-        <v>256</v>
+        <v>426</v>
       </c>
       <c r="D256" t="n">
         <v>2</v>
@@ -11457,7 +11457,7 @@
         <v>37913</v>
       </c>
       <c r="C257" t="n">
-        <v>341</v>
+        <v>511</v>
       </c>
       <c r="D257" t="n">
         <v>1</v>
@@ -11500,7 +11500,7 @@
         <v>37913</v>
       </c>
       <c r="C258" t="n">
-        <v>341</v>
+        <v>511</v>
       </c>
       <c r="D258" t="n">
         <v>2</v>
@@ -11543,7 +11543,7 @@
         <v>37913</v>
       </c>
       <c r="C259" t="n">
-        <v>426</v>
+        <v>596</v>
       </c>
       <c r="D259" t="n">
         <v>1</v>
@@ -11586,7 +11586,7 @@
         <v>37913</v>
       </c>
       <c r="C260" t="n">
-        <v>426</v>
+        <v>596</v>
       </c>
       <c r="D260" t="n">
         <v>2</v>
@@ -11629,7 +11629,7 @@
         <v>37913</v>
       </c>
       <c r="C261" t="n">
-        <v>511</v>
+        <v>681</v>
       </c>
       <c r="D261" t="n">
         <v>1</v>
@@ -11672,7 +11672,7 @@
         <v>37913</v>
       </c>
       <c r="C262" t="n">
-        <v>511</v>
+        <v>681</v>
       </c>
       <c r="D262" t="n">
         <v>2</v>
@@ -11715,7 +11715,7 @@
         <v>37913</v>
       </c>
       <c r="C263" t="n">
-        <v>596</v>
+        <v>766</v>
       </c>
       <c r="D263" t="n">
         <v>1</v>
@@ -11737,7 +11737,7 @@
         <v>45982</v>
       </c>
       <c r="I263" t="n">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>37913</v>
       </c>
       <c r="C264" t="n">
-        <v>596</v>
+        <v>766</v>
       </c>
       <c r="D264" t="n">
         <v>2</v>
@@ -11780,7 +11780,7 @@
         <v>45982</v>
       </c>
       <c r="I264" t="n">
-        <v>0.517</v>
+        <v>0.55</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>37913</v>
       </c>
       <c r="C265" t="n">
-        <v>681</v>
+        <v>865</v>
       </c>
       <c r="D265" t="n">
         <v>1</v>
@@ -11823,7 +11823,7 @@
         <v>45982</v>
       </c>
       <c r="I265" t="n">
-        <v>1.53</v>
+        <v>0.333</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -11841,36 +11841,36 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>37913</v>
+        <v>37973</v>
       </c>
       <c r="C266" t="n">
-        <v>681</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="I266" t="n">
-        <v>0.517</v>
+        <v>3.05</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -11884,36 +11884,36 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>37913</v>
+        <v>37973</v>
       </c>
       <c r="C267" t="n">
-        <v>766</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="I267" t="n">
-        <v>2.42</v>
+        <v>0.45</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -11927,36 +11927,36 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>37913</v>
+        <v>38013</v>
       </c>
       <c r="C268" t="n">
-        <v>766</v>
+        <v>1</v>
       </c>
       <c r="D268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="I268" t="n">
-        <v>0.55</v>
+        <v>1.5</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -11970,10 +11970,10 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>37913</v>
+        <v>38042</v>
       </c>
       <c r="C269" t="n">
-        <v>865</v>
+        <v>1</v>
       </c>
       <c r="D269" t="n">
         <v>1</v>
@@ -11989,13 +11989,13 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="I269" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -12013,10 +12013,10 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>37973</v>
+        <v>38042</v>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D270" t="n">
         <v>1</v>
@@ -12032,13 +12032,13 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="I270" t="n">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -12056,36 +12056,36 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>37973</v>
+        <v>38043</v>
       </c>
       <c r="C271" t="n">
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="I271" t="n">
-        <v>0.45</v>
+        <v>2.42</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -12099,22 +12099,22 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>38013</v>
+        <v>38043</v>
       </c>
       <c r="C272" t="n">
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G272" s="2" t="n">
@@ -12124,11 +12124,11 @@
         <v>45986</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5</v>
+        <v>0.55</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -12142,10 +12142,10 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>38042</v>
+        <v>38043</v>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D273" t="n">
         <v>1</v>
@@ -12167,7 +12167,7 @@
         <v>45986</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>2.42</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -12185,22 +12185,22 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>38042</v>
+        <v>38043</v>
       </c>
       <c r="C274" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G274" s="2" t="n">
@@ -12210,11 +12210,11 @@
         <v>45986</v>
       </c>
       <c r="I274" t="n">
-        <v>1.9</v>
+        <v>0.55</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -12231,7 +12231,7 @@
         <v>38043</v>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
@@ -12274,7 +12274,7 @@
         <v>38043</v>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="D276" t="n">
         <v>2</v>
@@ -12317,7 +12317,7 @@
         <v>38043</v>
       </c>
       <c r="C277" t="n">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="D277" t="n">
         <v>1</v>
@@ -12339,7 +12339,7 @@
         <v>45986</v>
       </c>
       <c r="I277" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>38043</v>
       </c>
       <c r="C278" t="n">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="D278" t="n">
         <v>2</v>
@@ -12382,7 +12382,7 @@
         <v>45986</v>
       </c>
       <c r="I278" t="n">
-        <v>0.55</v>
+        <v>0.583</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>38043</v>
       </c>
       <c r="C279" t="n">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="D279" t="n">
         <v>1</v>
@@ -12425,7 +12425,7 @@
         <v>45986</v>
       </c>
       <c r="I279" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>38043</v>
       </c>
       <c r="C280" t="n">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="D280" t="n">
         <v>2</v>
@@ -12468,7 +12468,7 @@
         <v>45986</v>
       </c>
       <c r="I280" t="n">
-        <v>0.55</v>
+        <v>0.583</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>38043</v>
       </c>
       <c r="C281" t="n">
-        <v>298</v>
+        <v>500</v>
       </c>
       <c r="D281" t="n">
         <v>1</v>
@@ -12532,7 +12532,7 @@
         <v>38043</v>
       </c>
       <c r="C282" t="n">
-        <v>298</v>
+        <v>500</v>
       </c>
       <c r="D282" t="n">
         <v>2</v>
@@ -12575,7 +12575,7 @@
         <v>38043</v>
       </c>
       <c r="C283" t="n">
-        <v>399</v>
+        <v>601</v>
       </c>
       <c r="D283" t="n">
         <v>1</v>
@@ -12618,7 +12618,7 @@
         <v>38043</v>
       </c>
       <c r="C284" t="n">
-        <v>399</v>
+        <v>601</v>
       </c>
       <c r="D284" t="n">
         <v>2</v>
@@ -12661,7 +12661,7 @@
         <v>38043</v>
       </c>
       <c r="C285" t="n">
-        <v>500</v>
+        <v>702</v>
       </c>
       <c r="D285" t="n">
         <v>1</v>
@@ -12704,7 +12704,7 @@
         <v>38043</v>
       </c>
       <c r="C286" t="n">
-        <v>500</v>
+        <v>702</v>
       </c>
       <c r="D286" t="n">
         <v>2</v>
@@ -12747,7 +12747,7 @@
         <v>38043</v>
       </c>
       <c r="C287" t="n">
-        <v>601</v>
+        <v>803</v>
       </c>
       <c r="D287" t="n">
         <v>1</v>
@@ -12790,7 +12790,7 @@
         <v>38043</v>
       </c>
       <c r="C288" t="n">
-        <v>601</v>
+        <v>803</v>
       </c>
       <c r="D288" t="n">
         <v>2</v>
@@ -12833,7 +12833,7 @@
         <v>38043</v>
       </c>
       <c r="C289" t="n">
-        <v>702</v>
+        <v>904</v>
       </c>
       <c r="D289" t="n">
         <v>1</v>
@@ -12855,7 +12855,7 @@
         <v>45986</v>
       </c>
       <c r="I289" t="n">
-        <v>2.46</v>
+        <v>3.53</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>38043</v>
       </c>
       <c r="C290" t="n">
-        <v>702</v>
+        <v>904</v>
       </c>
       <c r="D290" t="n">
         <v>2</v>
@@ -12898,7 +12898,7 @@
         <v>45986</v>
       </c>
       <c r="I290" t="n">
-        <v>0.583</v>
+        <v>0.45</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -12916,10 +12916,10 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>38043</v>
+        <v>38084</v>
       </c>
       <c r="C291" t="n">
-        <v>803</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
         <v>1</v>
@@ -12935,13 +12935,13 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="I291" t="n">
-        <v>2.46</v>
+        <v>1</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -12959,36 +12959,36 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>38043</v>
+        <v>38084</v>
       </c>
       <c r="C292" t="n">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="I292" t="n">
-        <v>0.583</v>
+        <v>1.267</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -13002,10 +13002,10 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>38043</v>
+        <v>38084</v>
       </c>
       <c r="C293" t="n">
-        <v>904</v>
+        <v>28</v>
       </c>
       <c r="D293" t="n">
         <v>1</v>
@@ -13021,13 +13021,13 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="I293" t="n">
-        <v>3.53</v>
+        <v>0.333</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -13045,36 +13045,36 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>38043</v>
+        <v>38084</v>
       </c>
       <c r="C294" t="n">
-        <v>904</v>
+        <v>36</v>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="I294" t="n">
-        <v>0.45</v>
+        <v>0.167</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -13091,7 +13091,7 @@
         <v>38084</v>
       </c>
       <c r="C295" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D295" t="n">
         <v>1</v>
@@ -13113,7 +13113,7 @@
         <v>45987</v>
       </c>
       <c r="I295" t="n">
-        <v>1</v>
+        <v>0.167</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>38084</v>
       </c>
       <c r="C296" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D296" t="n">
         <v>1</v>
@@ -13156,7 +13156,7 @@
         <v>45987</v>
       </c>
       <c r="I296" t="n">
-        <v>1.267</v>
+        <v>6.167</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -13174,10 +13174,10 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>38084</v>
+        <v>38085</v>
       </c>
       <c r="C297" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D297" t="n">
         <v>1</v>
@@ -13199,7 +13199,7 @@
         <v>45987</v>
       </c>
       <c r="I297" t="n">
-        <v>0.333</v>
+        <v>2.42</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -13217,22 +13217,22 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>38084</v>
+        <v>38085</v>
       </c>
       <c r="C298" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G298" s="2" t="n">
@@ -13242,11 +13242,11 @@
         <v>45987</v>
       </c>
       <c r="I298" t="n">
-        <v>0.167</v>
+        <v>0.55</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -13260,10 +13260,10 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>38084</v>
+        <v>38085</v>
       </c>
       <c r="C299" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="D299" t="n">
         <v>1</v>
@@ -13285,7 +13285,7 @@
         <v>45987</v>
       </c>
       <c r="I299" t="n">
-        <v>0.167</v>
+        <v>2.42</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -13303,22 +13303,22 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>38084</v>
+        <v>38085</v>
       </c>
       <c r="C300" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G300" s="2" t="n">
@@ -13328,11 +13328,11 @@
         <v>45987</v>
       </c>
       <c r="I300" t="n">
-        <v>6.167</v>
+        <v>0.55</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -13349,7 +13349,7 @@
         <v>38085</v>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="D301" t="n">
         <v>1</v>
@@ -13392,7 +13392,7 @@
         <v>38085</v>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="D302" t="n">
         <v>2</v>
@@ -13435,7 +13435,7 @@
         <v>38085</v>
       </c>
       <c r="C303" t="n">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="D303" t="n">
         <v>1</v>
@@ -13457,7 +13457,7 @@
         <v>45987</v>
       </c>
       <c r="I303" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>38085</v>
       </c>
       <c r="C304" t="n">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="D304" t="n">
         <v>2</v>
@@ -13500,7 +13500,7 @@
         <v>45987</v>
       </c>
       <c r="I304" t="n">
-        <v>0.55</v>
+        <v>0.583</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>38085</v>
       </c>
       <c r="C305" t="n">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="D305" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         <v>45987</v>
       </c>
       <c r="I305" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>38085</v>
       </c>
       <c r="C306" t="n">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="D306" t="n">
         <v>2</v>
@@ -13586,7 +13586,7 @@
         <v>45987</v>
       </c>
       <c r="I306" t="n">
-        <v>0.55</v>
+        <v>0.583</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>38085</v>
       </c>
       <c r="C307" t="n">
-        <v>298</v>
+        <v>500</v>
       </c>
       <c r="D307" t="n">
         <v>1</v>
@@ -13650,7 +13650,7 @@
         <v>38085</v>
       </c>
       <c r="C308" t="n">
-        <v>298</v>
+        <v>500</v>
       </c>
       <c r="D308" t="n">
         <v>2</v>
@@ -13693,7 +13693,7 @@
         <v>38085</v>
       </c>
       <c r="C309" t="n">
-        <v>399</v>
+        <v>601</v>
       </c>
       <c r="D309" t="n">
         <v>1</v>
@@ -13736,7 +13736,7 @@
         <v>38085</v>
       </c>
       <c r="C310" t="n">
-        <v>399</v>
+        <v>601</v>
       </c>
       <c r="D310" t="n">
         <v>2</v>
@@ -13779,7 +13779,7 @@
         <v>38085</v>
       </c>
       <c r="C311" t="n">
-        <v>500</v>
+        <v>702</v>
       </c>
       <c r="D311" t="n">
         <v>1</v>
@@ -13801,7 +13801,7 @@
         <v>45987</v>
       </c>
       <c r="I311" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>38085</v>
       </c>
       <c r="C312" t="n">
-        <v>500</v>
+        <v>702</v>
       </c>
       <c r="D312" t="n">
         <v>2</v>
@@ -13844,7 +13844,7 @@
         <v>45987</v>
       </c>
       <c r="I312" t="n">
-        <v>0.583</v>
+        <v>0.517</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>38085</v>
       </c>
       <c r="C313" t="n">
-        <v>601</v>
+        <v>787</v>
       </c>
       <c r="D313" t="n">
         <v>1</v>
@@ -13887,7 +13887,7 @@
         <v>45987</v>
       </c>
       <c r="I313" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>38085</v>
       </c>
       <c r="C314" t="n">
-        <v>601</v>
+        <v>787</v>
       </c>
       <c r="D314" t="n">
         <v>2</v>
@@ -13930,7 +13930,7 @@
         <v>45987</v>
       </c>
       <c r="I314" t="n">
-        <v>0.583</v>
+        <v>0.517</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>38085</v>
       </c>
       <c r="C315" t="n">
-        <v>702</v>
+        <v>872</v>
       </c>
       <c r="D315" t="n">
         <v>1</v>
@@ -13994,7 +13994,7 @@
         <v>38085</v>
       </c>
       <c r="C316" t="n">
-        <v>702</v>
+        <v>872</v>
       </c>
       <c r="D316" t="n">
         <v>2</v>
@@ -14037,7 +14037,7 @@
         <v>38085</v>
       </c>
       <c r="C317" t="n">
-        <v>787</v>
+        <v>957</v>
       </c>
       <c r="D317" t="n">
         <v>1</v>
@@ -14080,7 +14080,7 @@
         <v>38085</v>
       </c>
       <c r="C318" t="n">
-        <v>787</v>
+        <v>957</v>
       </c>
       <c r="D318" t="n">
         <v>2</v>
@@ -14120,17 +14120,17 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>38085</v>
+        <v>38086</v>
       </c>
       <c r="C319" t="n">
-        <v>872</v>
+        <v>1</v>
       </c>
       <c r="D319" t="n">
         <v>1</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>SAL</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -14145,11 +14145,11 @@
         <v>45987</v>
       </c>
       <c r="I319" t="n">
-        <v>1.53</v>
+        <v>0.733</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>SALDATURA</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -14163,22 +14163,22 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>38085</v>
+        <v>38086</v>
       </c>
       <c r="C320" t="n">
-        <v>872</v>
+        <v>4</v>
       </c>
       <c r="D320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G320" s="2" t="n">
@@ -14188,11 +14188,11 @@
         <v>45987</v>
       </c>
       <c r="I320" t="n">
-        <v>0.517</v>
+        <v>1.2</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>CABLAGGIO</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -14206,17 +14206,17 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>38085</v>
+        <v>38086</v>
       </c>
       <c r="C321" t="n">
-        <v>957</v>
+        <v>11</v>
       </c>
       <c r="D321" t="n">
         <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>SAL</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -14231,11 +14231,11 @@
         <v>45987</v>
       </c>
       <c r="I321" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>SALDATURA</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -14249,22 +14249,22 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>38085</v>
+        <v>38086</v>
       </c>
       <c r="C322" t="n">
-        <v>957</v>
+        <v>16</v>
       </c>
       <c r="D322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SAL</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G322" s="2" t="n">
@@ -14274,11 +14274,11 @@
         <v>45987</v>
       </c>
       <c r="I322" t="n">
-        <v>0.517</v>
+        <v>3.333</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>SALDATURA</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -14295,14 +14295,14 @@
         <v>38086</v>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D323" t="n">
         <v>1</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>SAL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -14317,11 +14317,11 @@
         <v>45987</v>
       </c>
       <c r="I323" t="n">
-        <v>0.733</v>
+        <v>2.5</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>SALDATURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -14338,14 +14338,14 @@
         <v>38086</v>
       </c>
       <c r="C324" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D324" t="n">
         <v>1</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -14360,11 +14360,11 @@
         <v>45987</v>
       </c>
       <c r="I324" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>CABLAGGIO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -14378,41 +14378,41 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>38086</v>
+        <v>38096</v>
       </c>
       <c r="C325" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
         <v>1</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>SAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNIO</t>
         </is>
       </c>
       <c r="G325" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="I325" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>SALDATURA</t>
+          <t>TORNITURA</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -14421,41 +14421,41 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>38086</v>
+        <v>38096</v>
       </c>
       <c r="C326" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D326" t="n">
         <v>1</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>SAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNIO</t>
         </is>
       </c>
       <c r="G326" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="I326" t="n">
-        <v>3.333</v>
+        <v>5</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>SALDATURA</t>
+          <t>TORNITURA</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -14464,41 +14464,41 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>38086</v>
+        <v>38096</v>
       </c>
       <c r="C327" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D327" t="n">
         <v>1</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNIO</t>
         </is>
       </c>
       <c r="G327" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="H327" s="2" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="I327" t="n">
-        <v>2.5</v>
+        <v>15.867</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNITURA</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -14507,41 +14507,41 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>38086</v>
+        <v>38096</v>
       </c>
       <c r="C328" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D328" t="n">
         <v>1</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNIO</t>
         </is>
       </c>
       <c r="G328" s="2" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="H328" s="2" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="I328" t="n">
-        <v>3.5</v>
+        <v>15.867</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>TORNITURA</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -14550,7 +14550,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>38096</v>
+        <v>38142</v>
       </c>
       <c r="C329" t="n">
         <v>1</v>
@@ -14560,31 +14560,31 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>TORNIO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G329" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="H329" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="I329" t="n">
-        <v>1.667</v>
+        <v>3.05</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>TORNITURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -14593,41 +14593,41 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>38096</v>
+        <v>38142</v>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>TORNIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G330" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="H330" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="I330" t="n">
-        <v>5</v>
+        <v>0.45</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>TORNITURA</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -14636,41 +14636,41 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>38096</v>
+        <v>38154</v>
       </c>
       <c r="C331" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D331" t="n">
         <v>1</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>TORNIO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G331" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="I331" t="n">
-        <v>15.867</v>
+        <v>0.317</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>TORNITURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -14679,41 +14679,41 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>38096</v>
+        <v>38154</v>
       </c>
       <c r="C332" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D332" t="n">
         <v>1</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>TORNIO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G332" s="2" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="H332" s="2" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="I332" t="n">
-        <v>15.867</v>
+        <v>0.633</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>TORNITURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14722,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>38142</v>
+        <v>38155</v>
       </c>
       <c r="C333" t="n">
         <v>1</v>
@@ -14747,7 +14747,7 @@
         <v>45989</v>
       </c>
       <c r="I333" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>38142</v>
+        <v>38155</v>
       </c>
       <c r="C334" t="n">
         <v>1</v>
@@ -14790,7 +14790,7 @@
         <v>45989</v>
       </c>
       <c r="I334" t="n">
-        <v>0.45</v>
+        <v>0.583</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -14808,10 +14808,10 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>38154</v>
+        <v>38155</v>
       </c>
       <c r="C335" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D335" t="n">
         <v>1</v>
@@ -14833,7 +14833,7 @@
         <v>45989</v>
       </c>
       <c r="I335" t="n">
-        <v>0.317</v>
+        <v>2.46</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -14851,22 +14851,22 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>38154</v>
+        <v>38155</v>
       </c>
       <c r="C336" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G336" s="2" t="n">
@@ -14876,11 +14876,11 @@
         <v>45989</v>
       </c>
       <c r="I336" t="n">
-        <v>0.633</v>
+        <v>0.583</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -14897,7 +14897,7 @@
         <v>38155</v>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="D337" t="n">
         <v>1</v>
@@ -14940,7 +14940,7 @@
         <v>38155</v>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="D338" t="n">
         <v>2</v>
@@ -14980,10 +14980,10 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>38155</v>
+        <v>38171</v>
       </c>
       <c r="C339" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="D339" t="n">
         <v>1</v>
@@ -15005,7 +15005,7 @@
         <v>45989</v>
       </c>
       <c r="I339" t="n">
-        <v>2.46</v>
+        <v>0.133</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -15023,22 +15023,22 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>38155</v>
+        <v>38171</v>
       </c>
       <c r="C340" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G340" s="2" t="n">
@@ -15048,11 +15048,11 @@
         <v>45989</v>
       </c>
       <c r="I340" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -15066,41 +15066,41 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>38155</v>
+        <v>38220</v>
       </c>
       <c r="C341" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
         <v>1</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G341" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H341" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="I341" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -15109,41 +15109,41 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>38155</v>
+        <v>38227</v>
       </c>
       <c r="C342" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>STOZZATRICE</t>
         </is>
       </c>
       <c r="G342" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H342" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="I342" t="n">
-        <v>0.583</v>
+        <v>1.33</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>STOZZATURA</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -15152,41 +15152,41 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>38171</v>
+        <v>38227</v>
       </c>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D343" t="n">
         <v>1</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>STO</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>STOZZATRICE</t>
         </is>
       </c>
       <c r="G343" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H343" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="I343" t="n">
-        <v>0.133</v>
+        <v>1.3</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>STOZZATURA</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -15195,41 +15195,41 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>38171</v>
+        <v>38227</v>
       </c>
       <c r="C344" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D344" t="n">
         <v>1</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>RTF</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>RETTIFICA</t>
         </is>
       </c>
       <c r="G344" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H344" s="2" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>RETTIFICA</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -15238,22 +15238,22 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>38220</v>
+        <v>38227</v>
       </c>
       <c r="C345" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D345" t="n">
         <v>1</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>RTF</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>RETTIFICA</t>
         </is>
       </c>
       <c r="G345" s="2" t="n">
@@ -15263,11 +15263,11 @@
         <v>45992</v>
       </c>
       <c r="I345" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>RETTIFICA</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -15284,33 +15284,33 @@
         <v>38227</v>
       </c>
       <c r="C346" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D346" t="n">
         <v>1</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>STOZZATRICE</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G346" s="2" t="n">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="H346" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I346" t="n">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>STOZZATURA</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -15327,33 +15327,33 @@
         <v>38227</v>
       </c>
       <c r="C347" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D347" t="n">
         <v>1</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>STO</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>STOZZATRICE</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G347" s="2" t="n">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="H347" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I347" t="n">
-        <v>1.3</v>
+        <v>15</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>STOZZATURA</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -15367,22 +15367,22 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>38227</v>
+        <v>38228</v>
       </c>
       <c r="C348" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D348" t="n">
         <v>1</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>RTF</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>RETTIFICA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G348" s="2" t="n">
@@ -15392,16 +15392,16 @@
         <v>45992</v>
       </c>
       <c r="I348" t="n">
-        <v>1.33</v>
+        <v>0.317</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>RETTIFICA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -15410,22 +15410,22 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>38227</v>
+        <v>38229</v>
       </c>
       <c r="C349" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D349" t="n">
         <v>1</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>RTF</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>RETTIFICA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G349" s="2" t="n">
@@ -15435,16 +15435,16 @@
         <v>45992</v>
       </c>
       <c r="I349" t="n">
-        <v>1.3</v>
+        <v>2.46</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>RETTIFICA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -15453,41 +15453,41 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>38227</v>
+        <v>38229</v>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G350" s="2" t="n">
-        <v>45988</v>
+        <v>45992</v>
       </c>
       <c r="H350" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I350" t="n">
-        <v>15</v>
+        <v>0.583</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -15496,41 +15496,41 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>38227</v>
+        <v>38251</v>
       </c>
       <c r="C351" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
         <v>1</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>FRE</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G351" s="2" t="n">
-        <v>45988</v>
+        <v>45993</v>
       </c>
       <c r="H351" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="I351" t="n">
-        <v>15</v>
+        <v>2.533</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>FRESATURA</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>38228</v>
+        <v>38252</v>
       </c>
       <c r="C352" t="n">
         <v>1</v>
@@ -15558,13 +15558,13 @@
         </is>
       </c>
       <c r="G352" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H352" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="I352" t="n">
-        <v>0.317</v>
+        <v>2.46</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -15582,36 +15582,36 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>38229</v>
+        <v>38252</v>
       </c>
       <c r="C353" t="n">
         <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G353" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H353" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="I353" t="n">
-        <v>2.46</v>
+        <v>0.583</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -15625,36 +15625,36 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>38229</v>
+        <v>38252</v>
       </c>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G354" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="I354" t="n">
-        <v>0.583</v>
+        <v>2.46</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -15668,22 +15668,22 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>38251</v>
+        <v>38252</v>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G355" s="2" t="n">
@@ -15693,11 +15693,11 @@
         <v>45993</v>
       </c>
       <c r="I355" t="n">
-        <v>2.533</v>
+        <v>0.583</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -15714,7 +15714,7 @@
         <v>38252</v>
       </c>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -15757,7 +15757,7 @@
         <v>38252</v>
       </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D357" t="n">
         <v>2</v>
@@ -15800,7 +15800,7 @@
         <v>38252</v>
       </c>
       <c r="C358" t="n">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="D358" t="n">
         <v>1</v>
@@ -15843,7 +15843,7 @@
         <v>38252</v>
       </c>
       <c r="C359" t="n">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="D359" t="n">
         <v>2</v>
@@ -15886,7 +15886,7 @@
         <v>38252</v>
       </c>
       <c r="C360" t="n">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="D360" t="n">
         <v>1</v>
@@ -15929,7 +15929,7 @@
         <v>38252</v>
       </c>
       <c r="C361" t="n">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="D361" t="n">
         <v>2</v>
@@ -15972,7 +15972,7 @@
         <v>38252</v>
       </c>
       <c r="C362" t="n">
-        <v>304</v>
+        <v>506</v>
       </c>
       <c r="D362" t="n">
         <v>1</v>
@@ -16015,7 +16015,7 @@
         <v>38252</v>
       </c>
       <c r="C363" t="n">
-        <v>304</v>
+        <v>506</v>
       </c>
       <c r="D363" t="n">
         <v>2</v>
@@ -16058,7 +16058,7 @@
         <v>38252</v>
       </c>
       <c r="C364" t="n">
-        <v>405</v>
+        <v>607</v>
       </c>
       <c r="D364" t="n">
         <v>1</v>
@@ -16101,7 +16101,7 @@
         <v>38252</v>
       </c>
       <c r="C365" t="n">
-        <v>405</v>
+        <v>607</v>
       </c>
       <c r="D365" t="n">
         <v>2</v>
@@ -16144,7 +16144,7 @@
         <v>38252</v>
       </c>
       <c r="C366" t="n">
-        <v>506</v>
+        <v>708</v>
       </c>
       <c r="D366" t="n">
         <v>1</v>
@@ -16187,7 +16187,7 @@
         <v>38252</v>
       </c>
       <c r="C367" t="n">
-        <v>506</v>
+        <v>708</v>
       </c>
       <c r="D367" t="n">
         <v>2</v>
@@ -16227,10 +16227,10 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>38252</v>
+        <v>38268</v>
       </c>
       <c r="C368" t="n">
-        <v>607</v>
+        <v>1</v>
       </c>
       <c r="D368" t="n">
         <v>1</v>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="G368" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="I368" t="n">
-        <v>2.46</v>
+        <v>0.167</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -16270,36 +16270,36 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>38252</v>
+        <v>38270</v>
       </c>
       <c r="C369" t="n">
-        <v>607</v>
+        <v>1</v>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G369" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H369" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="I369" t="n">
-        <v>0.583</v>
+        <v>1.53</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -16313,36 +16313,36 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>38252</v>
+        <v>38270</v>
       </c>
       <c r="C370" t="n">
-        <v>708</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G370" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H370" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="I370" t="n">
-        <v>2.46</v>
+        <v>0.517</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -16356,36 +16356,36 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>38252</v>
+        <v>38270</v>
       </c>
       <c r="C371" t="n">
-        <v>708</v>
+        <v>86</v>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ASS</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="G371" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="I371" t="n">
-        <v>0.583</v>
+        <v>2.44</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>ASSEMBLAGGIO</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -16399,22 +16399,22 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>38268</v>
+        <v>38270</v>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="G372" s="2" t="n">
@@ -16424,11 +16424,11 @@
         <v>45994</v>
       </c>
       <c r="I372" t="n">
-        <v>0.167</v>
+        <v>0.4</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>COLLAUDO</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -16445,7 +16445,7 @@
         <v>38270</v>
       </c>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="D373" t="n">
         <v>1</v>
@@ -16467,7 +16467,7 @@
         <v>45994</v>
       </c>
       <c r="I373" t="n">
-        <v>1.53</v>
+        <v>2.44</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>38270</v>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="D374" t="n">
         <v>2</v>
@@ -16510,7 +16510,7 @@
         <v>45994</v>
       </c>
       <c r="I374" t="n">
-        <v>0.517</v>
+        <v>0.4</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>38270</v>
       </c>
       <c r="C375" t="n">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="D375" t="n">
         <v>1</v>
@@ -16553,7 +16553,7 @@
         <v>45994</v>
       </c>
       <c r="I375" t="n">
-        <v>2.44</v>
+        <v>3.53</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>38270</v>
       </c>
       <c r="C376" t="n">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="D376" t="n">
         <v>2</v>
@@ -16596,7 +16596,7 @@
         <v>45994</v>
       </c>
       <c r="I376" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>38270</v>
       </c>
       <c r="C377" t="n">
-        <v>177</v>
+        <v>375</v>
       </c>
       <c r="D377" t="n">
         <v>1</v>
@@ -16639,7 +16639,7 @@
         <v>45994</v>
       </c>
       <c r="I377" t="n">
-        <v>2.44</v>
+        <v>3.53</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>38270</v>
       </c>
       <c r="C378" t="n">
-        <v>177</v>
+        <v>375</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
@@ -16682,7 +16682,7 @@
         <v>45994</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -16700,41 +16700,41 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>38270</v>
+        <v>38332</v>
       </c>
       <c r="C379" t="n">
-        <v>268</v>
+        <v>1</v>
       </c>
       <c r="D379" t="n">
         <v>1</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G379" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H379" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="I379" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -16743,41 +16743,41 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>38270</v>
+        <v>38332</v>
       </c>
       <c r="C380" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G380" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="H380" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="I380" t="n">
-        <v>0.45</v>
+        <v>8.1</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>COLLAUDO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -16786,41 +16786,41 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>38270</v>
+        <v>38332</v>
       </c>
       <c r="C381" t="n">
-        <v>375</v>
+        <v>5</v>
       </c>
       <c r="D381" t="n">
         <v>1</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>ASS</t>
+          <t>FRE</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="G381" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="I381" t="n">
-        <v>3.53</v>
+        <v>8.1</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>ASSEMBLAGGIO</t>
+          <t>FRESATURA</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -16829,39 +16829,1888 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>38270</v>
+        <v>38343</v>
       </c>
       <c r="C382" t="n">
-        <v>375</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
+        <v>1</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="I382" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>381</v>
+      </c>
+      <c r="B383" t="n">
+        <v>38346</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>FRE</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>FRESA</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I383" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>FRESATURA</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>382</v>
+      </c>
+      <c r="B384" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I384" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>383</v>
+      </c>
+      <c r="B385" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C385" t="n">
+        <v>15</v>
+      </c>
+      <c r="D385" t="n">
+        <v>1</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B386" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C386" t="n">
+        <v>29</v>
+      </c>
+      <c r="D386" t="n">
+        <v>1</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>385</v>
+      </c>
+      <c r="B387" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C387" t="n">
+        <v>37</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>386</v>
+      </c>
+      <c r="B388" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C388" t="n">
+        <v>45</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>387</v>
+      </c>
+      <c r="B389" t="n">
+        <v>38362</v>
+      </c>
+      <c r="C389" t="n">
+        <v>53</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B390" t="n">
+        <v>38363</v>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+      <c r="D390" t="n">
+        <v>1</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I390" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>389</v>
+      </c>
+      <c r="B391" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="n">
+        <v>1</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I391" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="B392" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="n">
         <v>2</v>
       </c>
-      <c r="E382" t="inlineStr">
+      <c r="E392" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>COLLAUDO</t>
-        </is>
-      </c>
-      <c r="G382" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="H382" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="I382" t="n">
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I392" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>391</v>
+      </c>
+      <c r="B393" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C393" t="n">
+        <v>100</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I393" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B394" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C394" t="n">
+        <v>100</v>
+      </c>
+      <c r="D394" t="n">
+        <v>2</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>393</v>
+      </c>
+      <c r="B395" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C395" t="n">
+        <v>199</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>394</v>
+      </c>
+      <c r="B396" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C396" t="n">
+        <v>199</v>
+      </c>
+      <c r="D396" t="n">
+        <v>2</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>395</v>
+      </c>
+      <c r="B397" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C397" t="n">
+        <v>284</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>396</v>
+      </c>
+      <c r="B398" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C398" t="n">
+        <v>284</v>
+      </c>
+      <c r="D398" t="n">
+        <v>2</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>397</v>
+      </c>
+      <c r="B399" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C399" t="n">
+        <v>369</v>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I399" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>398</v>
+      </c>
+      <c r="B400" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C400" t="n">
+        <v>369</v>
+      </c>
+      <c r="D400" t="n">
+        <v>2</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I400" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>399</v>
+      </c>
+      <c r="B401" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C401" t="n">
+        <v>454</v>
+      </c>
+      <c r="D401" t="n">
+        <v>1</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B402" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C402" t="n">
+        <v>454</v>
+      </c>
+      <c r="D402" t="n">
+        <v>2</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I402" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="B403" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C403" t="n">
+        <v>540</v>
+      </c>
+      <c r="D403" t="n">
+        <v>1</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I403" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>402</v>
+      </c>
+      <c r="B404" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C404" t="n">
+        <v>540</v>
+      </c>
+      <c r="D404" t="n">
+        <v>2</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>403</v>
+      </c>
+      <c r="B405" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C405" t="n">
+        <v>625</v>
+      </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B406" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C406" t="n">
+        <v>625</v>
+      </c>
+      <c r="D406" t="n">
+        <v>2</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I406" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="B407" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C407" t="n">
+        <v>710</v>
+      </c>
+      <c r="D407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H407" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I407" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>406</v>
+      </c>
+      <c r="B408" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C408" t="n">
+        <v>710</v>
+      </c>
+      <c r="D408" t="n">
+        <v>2</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B409" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C409" t="n">
+        <v>795</v>
+      </c>
+      <c r="D409" t="n">
+        <v>1</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I409" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B410" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C410" t="n">
+        <v>795</v>
+      </c>
+      <c r="D410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>409</v>
+      </c>
+      <c r="B411" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C411" t="n">
+        <v>894</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I411" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="B412" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C412" t="n">
+        <v>894</v>
+      </c>
+      <c r="D412" t="n">
+        <v>2</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>411</v>
+      </c>
+      <c r="B413" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C413" t="n">
+        <v>993</v>
+      </c>
+      <c r="D413" t="n">
+        <v>1</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B414" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C414" t="n">
+        <v>993</v>
+      </c>
+      <c r="D414" t="n">
+        <v>2</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>413</v>
+      </c>
+      <c r="B415" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C415" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D415" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>414</v>
+      </c>
+      <c r="B416" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D416" t="n">
+        <v>2</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="B417" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C417" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D417" t="n">
+        <v>1</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I417" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="B418" t="n">
+        <v>38365</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D418" t="n">
+        <v>2</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I418" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>417</v>
+      </c>
+      <c r="B419" t="n">
+        <v>38375</v>
+      </c>
+      <c r="C419" t="n">
+        <v>1</v>
+      </c>
+      <c r="D419" t="n">
+        <v>1</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I419" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>418</v>
+      </c>
+      <c r="B420" t="n">
+        <v>38375</v>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D420" t="n">
+        <v>2</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I420" t="n">
         <v>0.45</v>
       </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>COLLAUDO</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr">
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>419</v>
+      </c>
+      <c r="B421" t="n">
+        <v>38375</v>
+      </c>
+      <c r="C421" t="n">
+        <v>104</v>
+      </c>
+      <c r="D421" t="n">
+        <v>1</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I421" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="B422" t="n">
+        <v>38375</v>
+      </c>
+      <c r="C422" t="n">
+        <v>104</v>
+      </c>
+      <c r="D422" t="n">
+        <v>2</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I422" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>421</v>
+      </c>
+      <c r="B423" t="n">
+        <v>38390</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>422</v>
+      </c>
+      <c r="B424" t="n">
+        <v>38391</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>ASS</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I424" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>ASSEMBLAGGIO</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>423</v>
+      </c>
+      <c r="B425" t="n">
+        <v>38391</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+      <c r="D425" t="n">
+        <v>2</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>COLLAUDO</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
         <is>
           <t>10</t>
         </is>
